--- a/src/test/resources/TestData/API_TestData.xlsx
+++ b/src/test/resources/TestData/API_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f771015cb644ad2/Desktop/TestData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:801_{161A3527-1944-4ACD-B13D-58C3359BB7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{590DA064-B831-4203-BD07-74D01C6AE991}"/>
+  <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:801_{161A3527-1944-4ACD-B13D-58C3359BB7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83FE7F7D-A782-4A38-B5FA-A93E1F0DB412}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{CCD3FC9E-7557-4CCE-88A9-77BB22194E14}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CCD3FC9E-7557-4CCE-88A9-77BB22194E14}"/>
   </bookViews>
   <sheets>
     <sheet name="Search" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="260" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="93">
   <si>
     <t>Code</t>
   </si>
@@ -84,9 +84,6 @@
     <t>Zip</t>
   </si>
   <si>
-    <t>Ethan</t>
-  </si>
-  <si>
     <t>10A-01</t>
   </si>
   <si>
@@ -159,9 +156,6 @@
     <t>India</t>
   </si>
   <si>
-    <t>ValidNam</t>
-  </si>
-  <si>
     <t>MichealHeww@gmail.com</t>
   </si>
   <si>
@@ -237,9 +231,6 @@
     <t>P1-73</t>
   </si>
   <si>
-    <t>P1-74</t>
-  </si>
-  <si>
     <t>santaclara</t>
   </si>
   <si>
@@ -303,16 +294,19 @@
     <t>HTTP/1.1 409 Conflict</t>
   </si>
   <si>
-    <t>Moolan</t>
-  </si>
-  <si>
-    <t>Moolan2012@gmail.com</t>
-  </si>
-  <si>
     <t xml:space="preserve"> HTTP/1.1 200 OK</t>
   </si>
   <si>
     <t>HTTP/1.1 405 Method Not Allowed</t>
+  </si>
+  <si>
+    <t>AlreadyExisting</t>
+  </si>
+  <si>
+    <t>GeorgeSam</t>
+  </si>
+  <si>
+    <t>HTTP/1.1 400 Bad Request</t>
   </si>
 </sst>
 </file>
@@ -718,7 +712,7 @@
         <v>401</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -729,7 +723,7 @@
         <v>401</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -740,10 +734,10 @@
         <v>401</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -751,7 +745,7 @@
         <v>404</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -762,7 +756,7 @@
         <v>404</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -773,7 +767,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -836,28 +830,28 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C2" s="2">
         <v>7865431245</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F2" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" t="s">
         <v>70</v>
       </c>
-      <c r="G2" t="s">
-        <v>73</v>
-      </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I2">
         <v>65432</v>
@@ -866,7 +860,7 @@
         <v>201</v>
       </c>
       <c r="K2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L2" t="s">
         <v>7</v>
@@ -874,28 +868,28 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C3" s="2">
         <v>7357950300</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3">
         <v>65432</v>
@@ -904,7 +898,7 @@
         <v>401</v>
       </c>
       <c r="K3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L3" t="s">
         <v>4</v>
@@ -912,28 +906,28 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C4" s="2">
         <v>7357911100</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4">
         <v>65432</v>
@@ -942,7 +936,7 @@
         <v>401</v>
       </c>
       <c r="K4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L4" t="s">
         <v>3</v>
@@ -950,28 +944,28 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C5" s="2">
         <v>7357950302</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G5" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I5">
         <v>65432</v>
@@ -980,36 +974,36 @@
         <v>401</v>
       </c>
       <c r="K5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C6" s="2">
         <v>7357950301</v>
       </c>
       <c r="D6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I6">
         <v>65432</v>
@@ -1018,7 +1012,7 @@
         <v>404</v>
       </c>
       <c r="K6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L6" t="s">
         <v>5</v>
@@ -1026,28 +1020,28 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C7" s="2">
         <v>7357950303</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I7">
         <v>65432</v>
@@ -1056,7 +1050,7 @@
         <v>404</v>
       </c>
       <c r="K7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L7" t="s">
         <v>6</v>
@@ -1064,28 +1058,28 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C8" s="2">
         <v>7865431245</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E8" t="s">
+        <v>65</v>
+      </c>
+      <c r="F8" t="s">
         <v>67</v>
       </c>
-      <c r="F8" t="s">
-        <v>70</v>
-      </c>
       <c r="G8" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="H8" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I8">
         <v>65432</v>
@@ -1094,10 +1088,10 @@
         <v>409</v>
       </c>
       <c r="K8" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="L8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
@@ -1105,37 +1099,37 @@
         <v>91</v>
       </c>
       <c r="B9" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9">
+        <v>9183618476</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="2">
-        <v>7065032286</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="E9" t="s">
-        <v>69</v>
-      </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>19</v>
       </c>
       <c r="G9" t="s">
-        <v>73</v>
+        <v>20</v>
       </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I9">
-        <v>65432</v>
+        <v>98765</v>
       </c>
       <c r="J9">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K9" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="L9" t="s">
-        <v>43</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1143,11 +1137,11 @@
   <hyperlinks>
     <hyperlink ref="D8" r:id="rId1" xr:uid="{098AB883-4330-4EB4-A999-3A4F81E17B5D}"/>
     <hyperlink ref="D2" r:id="rId2" xr:uid="{E9FC5BAC-CB68-44E8-AFDE-2F5238E72CCF}"/>
-    <hyperlink ref="D9" r:id="rId3" xr:uid="{55A19A57-C7F2-46D7-B8DD-D6C017CD509C}"/>
-    <hyperlink ref="D3" r:id="rId4" xr:uid="{82C6708F-047B-4F8B-9597-DED421052CCC}"/>
-    <hyperlink ref="D5" r:id="rId5" xr:uid="{4C248026-2F89-42F2-97F5-7C84561EFCDF}"/>
-    <hyperlink ref="D7" r:id="rId6" xr:uid="{C0E6EDBA-CDF8-44BA-A841-FBAB059CAF08}"/>
-    <hyperlink ref="D4" r:id="rId7" xr:uid="{D81A4EA9-F4B0-4942-89FD-86EB42708B39}"/>
+    <hyperlink ref="D3" r:id="rId3" xr:uid="{82C6708F-047B-4F8B-9597-DED421052CCC}"/>
+    <hyperlink ref="D5" r:id="rId4" xr:uid="{4C248026-2F89-42F2-97F5-7C84561EFCDF}"/>
+    <hyperlink ref="D7" r:id="rId5" xr:uid="{C0E6EDBA-CDF8-44BA-A841-FBAB059CAF08}"/>
+    <hyperlink ref="D4" r:id="rId6" xr:uid="{D81A4EA9-F4B0-4942-89FD-86EB42708B39}"/>
+    <hyperlink ref="D9" r:id="rId7" display="Bartholome_Schaefer2@hotmail.com" xr:uid="{1562BBC1-A157-46CA-9FBB-EF3A28ACB0E8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1155,14 +1149,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECED621D-DECE-49F3-A155-EDAA9CC71B01}">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
     <col min="3" max="3" width="13.46484375" customWidth="1"/>
     <col min="4" max="4" width="31.46484375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7.796875" customWidth="1"/>
-    <col min="11" max="11" width="19.86328125" customWidth="1"/>
+    <col min="11" max="11" width="26.53125" customWidth="1"/>
     <col min="12" max="12" width="17.86328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1206,28 +1200,28 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C2">
         <v>9183618476</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
         <v>19</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
-        <v>21</v>
-      </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I2">
         <v>98765</v>
@@ -1236,7 +1230,7 @@
         <v>200</v>
       </c>
       <c r="K2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L2" t="s">
         <v>7</v>
@@ -1247,25 +1241,25 @@
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C3">
-        <v>9183618477</v>
+        <v>9183618476</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" t="s">
         <v>19</v>
       </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
       <c r="H3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I3">
         <v>98765</v>
@@ -1274,33 +1268,36 @@
         <v>400</v>
       </c>
       <c r="K3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>31</v>
+      </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4">
-        <v>9183618478</v>
+        <v>9183618477</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
         <v>19</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>20</v>
       </c>
-      <c r="G4" t="s">
-        <v>21</v>
-      </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4">
         <v>98765</v>
@@ -1309,36 +1306,33 @@
         <v>400</v>
       </c>
       <c r="K4" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>33</v>
-      </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C5">
-        <v>9183618479</v>
+        <v>9183618478</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E5" t="s">
+        <v>18</v>
+      </c>
+      <c r="F5" t="s">
         <v>19</v>
       </c>
-      <c r="F5" t="s">
+      <c r="G5" t="s">
         <v>20</v>
       </c>
-      <c r="G5" t="s">
-        <v>21</v>
-      </c>
       <c r="H5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I5">
         <v>98765</v>
@@ -1347,36 +1341,36 @@
         <v>400</v>
       </c>
       <c r="K5" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="L5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" t="s">
         <v>33</v>
       </c>
-      <c r="B6" t="s">
-        <v>35</v>
-      </c>
       <c r="C6">
-        <v>9183618480</v>
+        <v>9183618479</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="E6" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" t="s">
         <v>19</v>
       </c>
-      <c r="F6" t="s">
+      <c r="G6" t="s">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
-        <v>21</v>
-      </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I6">
         <v>98765</v>
@@ -1385,33 +1379,36 @@
         <v>400</v>
       </c>
       <c r="K6" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="L6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>34</v>
       </c>
       <c r="C7">
-        <v>9183618481</v>
+        <v>9183618480</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" t="s">
         <v>19</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>20</v>
       </c>
-      <c r="G7" t="s">
-        <v>21</v>
-      </c>
       <c r="H7" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I7">
         <v>98765</v>
@@ -1420,36 +1417,33 @@
         <v>400</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="L7" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>879183618482</v>
+        <v>9183618481</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s">
         <v>19</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>20</v>
       </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
       <c r="H8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I8">
         <v>98765</v>
@@ -1458,36 +1452,36 @@
         <v>400</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="L8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9">
-        <v>45938476</v>
+        <v>879183618482</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
         <v>19</v>
       </c>
-      <c r="F9" t="s">
+      <c r="G9" t="s">
         <v>20</v>
       </c>
-      <c r="G9" t="s">
-        <v>21</v>
-      </c>
       <c r="H9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I9">
         <v>98765</v>
@@ -1496,33 +1490,36 @@
         <v>400</v>
       </c>
       <c r="K9" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="L9" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="C10">
+        <v>45938476</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
         <v>19</v>
       </c>
-      <c r="F10" t="s">
+      <c r="G10" t="s">
         <v>20</v>
       </c>
-      <c r="G10" t="s">
-        <v>21</v>
-      </c>
       <c r="H10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I10">
         <v>98765</v>
@@ -1531,33 +1528,33 @@
         <v>400</v>
       </c>
       <c r="K10" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="L10" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11">
-        <v>9183618483</v>
+        <v>29</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>51</v>
       </c>
       <c r="E11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F11" t="s">
         <v>19</v>
       </c>
-      <c r="F11" t="s">
+      <c r="G11" t="s">
         <v>20</v>
       </c>
-      <c r="G11" t="s">
-        <v>21</v>
-      </c>
       <c r="H11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I11">
         <v>98765</v>
@@ -1566,74 +1563,71 @@
         <v>400</v>
       </c>
       <c r="K11" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="L11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12">
-        <v>9183618484</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>54</v>
+        <v>9183618483</v>
       </c>
       <c r="E12" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" t="s">
         <v>19</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>20</v>
       </c>
-      <c r="G12" t="s">
-        <v>21</v>
-      </c>
       <c r="H12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I12">
         <v>98765</v>
       </c>
       <c r="J12">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K12" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="L12" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13">
-        <v>9183618485</v>
+        <v>9183618484</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
+        <v>18</v>
+      </c>
+      <c r="F13" t="s">
         <v>19</v>
       </c>
-      <c r="F13" t="s">
+      <c r="G13" t="s">
         <v>20</v>
       </c>
-      <c r="G13" t="s">
-        <v>21</v>
-      </c>
       <c r="H13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I13">
         <v>98765</v>
@@ -1642,142 +1636,181 @@
         <v>401</v>
       </c>
       <c r="K13" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="L13" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14">
-        <v>9183618486</v>
+        <v>9183618485</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
+        <v>18</v>
+      </c>
+      <c r="F14" t="s">
         <v>19</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
         <v>20</v>
       </c>
-      <c r="G14" t="s">
-        <v>21</v>
-      </c>
       <c r="H14" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I14">
         <v>98765</v>
       </c>
       <c r="J14">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="K14" t="s">
-        <v>40</v>
+        <v>82</v>
       </c>
       <c r="L14" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15">
-        <v>9183618487</v>
+        <v>9183618486</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s">
+        <v>18</v>
+      </c>
+      <c r="F15" t="s">
         <v>19</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>20</v>
       </c>
-      <c r="G15" t="s">
-        <v>21</v>
-      </c>
       <c r="H15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I15">
         <v>98765</v>
       </c>
       <c r="J15">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="K15" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="L15" t="s">
-        <v>36</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16">
-        <v>9183618488</v>
+        <v>9183618487</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E16" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s">
         <v>19</v>
       </c>
-      <c r="F16" t="s">
+      <c r="G16" t="s">
         <v>20</v>
       </c>
-      <c r="G16" t="s">
-        <v>21</v>
-      </c>
       <c r="H16" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I16">
         <v>98765</v>
       </c>
       <c r="J16">
+        <v>401</v>
+      </c>
+      <c r="K16" t="s">
+        <v>82</v>
+      </c>
+      <c r="L16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17">
+        <v>9183618488</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="E17" t="s">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17">
+        <v>98765</v>
+      </c>
+      <c r="J17">
         <v>400</v>
       </c>
-      <c r="K16" t="s">
-        <v>41</v>
-      </c>
-      <c r="L16" t="s">
+      <c r="K17" t="s">
+        <v>92</v>
+      </c>
+      <c r="L17" t="s">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="Bartholome_Schaefer2@hotmail.com" xr:uid="{851CD530-0F49-4D60-BAE6-8D3B1E28E4DF}"/>
-    <hyperlink ref="D3" r:id="rId2" display="Bartholome_Schaefer3@hotmail.com" xr:uid="{DA670D62-1310-44E1-A3B6-B7B7ECD7C1DC}"/>
-    <hyperlink ref="D4" r:id="rId3" display="Bartholome_Schaefer4@hotmail.com" xr:uid="{E5E8BBB8-174A-47BD-AF15-681FEC060066}"/>
-    <hyperlink ref="D5" r:id="rId4" display="Bartholome_Schaefer5@hotmail.com" xr:uid="{32158487-913F-4F35-9DDE-4B9D2B80E9D2}"/>
-    <hyperlink ref="D6" r:id="rId5" display="Bartholome_Schaefer6@hotmail.com" xr:uid="{508766D6-BBB4-4A82-81E2-E81C22B86965}"/>
-    <hyperlink ref="D7" r:id="rId6" display="Bartholome_Schaefer7@hotmail.com" xr:uid="{8E481797-25A1-41A9-BD58-75135C7D01DB}"/>
-    <hyperlink ref="D8" r:id="rId7" display="Bartholome_Schaefer8@hotmail.com" xr:uid="{05D9F043-3640-433A-93A6-27A7FB6C1F47}"/>
-    <hyperlink ref="D9" r:id="rId8" display="Bartholome_Schaefer9@hotmail.com" xr:uid="{4AD27C6A-21B7-4AD6-AFB9-F3A0BAB8CB8D}"/>
-    <hyperlink ref="D10" r:id="rId9" display="Bartholome_Schaefer12@hotmail.com" xr:uid="{DD758E89-7735-408E-A98A-E4D655F0868B}"/>
-    <hyperlink ref="D12" r:id="rId10" display="Bartholome_Schaefer13@hotmail.com" xr:uid="{6B542D06-ECE6-4EB0-9301-BFBAF2AF5188}"/>
-    <hyperlink ref="D13" r:id="rId11" display="Bartholome_Schaefer14@hotmail.com" xr:uid="{F594A674-A65C-406B-AB96-0D7DFD3AAB43}"/>
-    <hyperlink ref="D14" r:id="rId12" display="Bartholome_Schaefer15@hotmail.com" xr:uid="{A7710B21-5150-41F3-B0CC-49ACD30F2D9A}"/>
-    <hyperlink ref="D15" r:id="rId13" display="Bartholome_Schaefer16@hotmail.com" xr:uid="{0583EE08-AC79-4B30-A29B-D8FC172EFE45}"/>
-    <hyperlink ref="D16" r:id="rId14" display="Bartholome_Schaefer17@hotmail.com" xr:uid="{6DA339A0-459A-4004-9F0C-9C1E6F9441DE}"/>
+    <hyperlink ref="D4" r:id="rId2" display="Bartholome_Schaefer3@hotmail.com" xr:uid="{DA670D62-1310-44E1-A3B6-B7B7ECD7C1DC}"/>
+    <hyperlink ref="D5" r:id="rId3" display="Bartholome_Schaefer4@hotmail.com" xr:uid="{E5E8BBB8-174A-47BD-AF15-681FEC060066}"/>
+    <hyperlink ref="D6" r:id="rId4" display="Bartholome_Schaefer5@hotmail.com" xr:uid="{32158487-913F-4F35-9DDE-4B9D2B80E9D2}"/>
+    <hyperlink ref="D7" r:id="rId5" display="Bartholome_Schaefer6@hotmail.com" xr:uid="{508766D6-BBB4-4A82-81E2-E81C22B86965}"/>
+    <hyperlink ref="D8" r:id="rId6" display="Bartholome_Schaefer7@hotmail.com" xr:uid="{8E481797-25A1-41A9-BD58-75135C7D01DB}"/>
+    <hyperlink ref="D9" r:id="rId7" display="Bartholome_Schaefer8@hotmail.com" xr:uid="{05D9F043-3640-433A-93A6-27A7FB6C1F47}"/>
+    <hyperlink ref="D10" r:id="rId8" display="Bartholome_Schaefer9@hotmail.com" xr:uid="{4AD27C6A-21B7-4AD6-AFB9-F3A0BAB8CB8D}"/>
+    <hyperlink ref="D11" r:id="rId9" display="Bartholome_Schaefer12@hotmail.com" xr:uid="{DD758E89-7735-408E-A98A-E4D655F0868B}"/>
+    <hyperlink ref="D13" r:id="rId10" display="Bartholome_Schaefer13@hotmail.com" xr:uid="{6B542D06-ECE6-4EB0-9301-BFBAF2AF5188}"/>
+    <hyperlink ref="D14" r:id="rId11" display="Bartholome_Schaefer14@hotmail.com" xr:uid="{F594A674-A65C-406B-AB96-0D7DFD3AAB43}"/>
+    <hyperlink ref="D15" r:id="rId12" display="Bartholome_Schaefer15@hotmail.com" xr:uid="{A7710B21-5150-41F3-B0CC-49ACD30F2D9A}"/>
+    <hyperlink ref="D16" r:id="rId13" display="Bartholome_Schaefer16@hotmail.com" xr:uid="{0583EE08-AC79-4B30-A29B-D8FC172EFE45}"/>
+    <hyperlink ref="D17" r:id="rId14" display="Bartholome_Schaefer17@hotmail.com" xr:uid="{6DA339A0-459A-4004-9F0C-9C1E6F9441DE}"/>
+    <hyperlink ref="D3" r:id="rId15" display="Bartholome_Schaefer2@hotmail.com" xr:uid="{E8BE95CA-13CE-4DD6-940F-D7F4F5F30AF4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1808,7 +1841,7 @@
         <v>401</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -1819,7 +1852,7 @@
         <v>401</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -1830,10 +1863,10 @@
         <v>401</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.45">
@@ -1841,7 +1874,7 @@
         <v>404</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1852,7 +1885,7 @@
         <v>405</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -1863,7 +1896,7 @@
         <v>404</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -1874,7 +1907,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>

--- a/src/test/resources/TestData/API_TestData.xlsx
+++ b/src/test/resources/TestData/API_TestData.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f771015cb644ad2/Desktop/TestData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="105" documentId="13_ncr:801_{161A3527-1944-4ACD-B13D-58C3359BB7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83FE7F7D-A782-4A38-B5FA-A93E1F0DB412}"/>
+  <xr:revisionPtr revIDLastSave="116" documentId="13_ncr:801_{161A3527-1944-4ACD-B13D-58C3359BB7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{128CB197-CC8B-41DA-8124-55C96C9B7BD5}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CCD3FC9E-7557-4CCE-88A9-77BB22194E14}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="2" xr2:uid="{CCD3FC9E-7557-4CCE-88A9-77BB22194E14}"/>
   </bookViews>
   <sheets>
     <sheet name="Search" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="91">
   <si>
     <t>Code</t>
   </si>
@@ -144,13 +144,7 @@
     <t>CharFirstName</t>
   </si>
   <si>
-    <t xml:space="preserve">HTTP/1.1 200 </t>
-  </si>
-  <si>
     <t>HTTP/1.1 404 Not Found</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTTP/1.1 400 </t>
   </si>
   <si>
     <t>India</t>
@@ -712,7 +706,7 @@
         <v>401</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -723,7 +717,7 @@
         <v>401</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -734,7 +728,7 @@
         <v>401</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
@@ -745,7 +739,7 @@
         <v>404</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
         <v>5</v>
@@ -756,7 +750,7 @@
         <v>404</v>
       </c>
       <c r="B6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C6" t="s">
         <v>6</v>
@@ -767,7 +761,7 @@
         <v>200</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
@@ -830,25 +824,25 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C2" s="2">
         <v>7865431245</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H2" t="s">
         <v>21</v>
@@ -860,7 +854,7 @@
         <v>201</v>
       </c>
       <c r="K2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="L2" t="s">
         <v>7</v>
@@ -868,25 +862,25 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C3" s="2">
         <v>7357950300</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
         <v>21</v>
@@ -898,7 +892,7 @@
         <v>401</v>
       </c>
       <c r="K3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L3" t="s">
         <v>4</v>
@@ -906,25 +900,25 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2">
         <v>7357911100</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F4" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
         <v>21</v>
@@ -936,7 +930,7 @@
         <v>401</v>
       </c>
       <c r="K4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L4" t="s">
         <v>3</v>
@@ -944,25 +938,25 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C5" s="2">
         <v>7357950302</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H5" t="s">
         <v>21</v>
@@ -974,7 +968,7 @@
         <v>401</v>
       </c>
       <c r="K5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L5" t="s">
         <v>35</v>
@@ -982,25 +976,25 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C6" s="2">
         <v>7357950301</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
         <v>21</v>
@@ -1012,7 +1006,7 @@
         <v>404</v>
       </c>
       <c r="K6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L6" t="s">
         <v>5</v>
@@ -1020,25 +1014,25 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C7" s="2">
         <v>7357950303</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H7" t="s">
         <v>21</v>
@@ -1050,7 +1044,7 @@
         <v>404</v>
       </c>
       <c r="K7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L7" t="s">
         <v>6</v>
@@ -1058,28 +1052,28 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2">
         <v>7865431245</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E8" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" t="s">
         <v>65</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>67</v>
       </c>
-      <c r="G8" t="s">
-        <v>69</v>
-      </c>
       <c r="H8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="I8">
         <v>65432</v>
@@ -1088,7 +1082,7 @@
         <v>409</v>
       </c>
       <c r="K8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="L8" t="s">
         <v>30</v>
@@ -1096,7 +1090,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B9" t="s">
         <v>29</v>
@@ -1105,7 +1099,7 @@
         <v>9183618476</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
@@ -1123,10 +1117,10 @@
         <v>98765</v>
       </c>
       <c r="J9">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="K9" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="L9" t="s">
         <v>7</v>
@@ -1209,7 +1203,7 @@
         <v>9183618476</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
@@ -1230,7 +1224,7 @@
         <v>200</v>
       </c>
       <c r="K2" t="s">
-        <v>38</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s">
         <v>7</v>
@@ -1247,7 +1241,7 @@
         <v>9183618476</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -1265,13 +1259,13 @@
         <v>98765</v>
       </c>
       <c r="J3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="K3" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="L3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.45">
@@ -1285,7 +1279,7 @@
         <v>9183618477</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E4" t="s">
         <v>18</v>
@@ -1306,7 +1300,7 @@
         <v>400</v>
       </c>
       <c r="K4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L4" t="s">
         <v>37</v>
@@ -1320,7 +1314,7 @@
         <v>9183618478</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E5" t="s">
         <v>18</v>
@@ -1341,7 +1335,7 @@
         <v>400</v>
       </c>
       <c r="K5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L5" t="s">
         <v>22</v>
@@ -1358,7 +1352,7 @@
         <v>9183618479</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
         <v>18</v>
@@ -1379,7 +1373,7 @@
         <v>400</v>
       </c>
       <c r="K6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L6" t="s">
         <v>23</v>
@@ -1396,7 +1390,7 @@
         <v>9183618480</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -1417,7 +1411,7 @@
         <v>400</v>
       </c>
       <c r="K7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L7" t="s">
         <v>36</v>
@@ -1431,7 +1425,7 @@
         <v>9183618481</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E8" t="s">
         <v>18</v>
@@ -1452,7 +1446,7 @@
         <v>400</v>
       </c>
       <c r="K8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L8" t="s">
         <v>24</v>
@@ -1469,7 +1463,7 @@
         <v>879183618482</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
         <v>18</v>
@@ -1490,7 +1484,7 @@
         <v>400</v>
       </c>
       <c r="K9" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L9" t="s">
         <v>26</v>
@@ -1507,7 +1501,7 @@
         <v>45938476</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" t="s">
         <v>18</v>
@@ -1528,7 +1522,7 @@
         <v>400</v>
       </c>
       <c r="K10" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L10" t="s">
         <v>27</v>
@@ -1542,7 +1536,7 @@
         <v>29</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
         <v>18</v>
@@ -1563,7 +1557,7 @@
         <v>400</v>
       </c>
       <c r="K11" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L11" t="s">
         <v>28</v>
@@ -1598,7 +1592,7 @@
         <v>400</v>
       </c>
       <c r="K12" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L12" t="s">
         <v>25</v>
@@ -1615,7 +1609,7 @@
         <v>9183618484</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E13" t="s">
         <v>18</v>
@@ -1636,7 +1630,7 @@
         <v>401</v>
       </c>
       <c r="K13" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L13" t="s">
         <v>3</v>
@@ -1653,7 +1647,7 @@
         <v>9183618485</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E14" t="s">
         <v>18</v>
@@ -1674,7 +1668,7 @@
         <v>401</v>
       </c>
       <c r="K14" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L14" t="s">
         <v>4</v>
@@ -1691,7 +1685,7 @@
         <v>9183618486</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E15" t="s">
         <v>18</v>
@@ -1712,7 +1706,7 @@
         <v>404</v>
       </c>
       <c r="K15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L15" t="s">
         <v>6</v>
@@ -1729,7 +1723,7 @@
         <v>9183618487</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E16" t="s">
         <v>18</v>
@@ -1750,7 +1744,7 @@
         <v>401</v>
       </c>
       <c r="K16" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L16" t="s">
         <v>35</v>
@@ -1767,7 +1761,7 @@
         <v>9183618488</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E17" t="s">
         <v>18</v>
@@ -1788,7 +1782,7 @@
         <v>400</v>
       </c>
       <c r="K17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="L17" t="s">
         <v>5</v>
@@ -1841,7 +1835,7 @@
         <v>401</v>
       </c>
       <c r="B2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -1852,7 +1846,7 @@
         <v>401</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
         <v>4</v>
@@ -1863,7 +1857,7 @@
         <v>401</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C4" t="s">
         <v>35</v>
@@ -1874,7 +1868,7 @@
         <v>404</v>
       </c>
       <c r="B5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
         <v>6</v>
@@ -1885,7 +1879,7 @@
         <v>405</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
         <v>5</v>
@@ -1896,7 +1890,7 @@
         <v>404</v>
       </c>
       <c r="B7" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
         <v>8</v>
@@ -1907,7 +1901,7 @@
         <v>200</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
